--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0008_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0008_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -63,7 +64,7 @@
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="14.7109375" customWidth="true"/>
     <col min="7" max="7" width="13.7109375" customWidth="true"/>
-    <col min="8" max="8" width="13.7109375" customWidth="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true"/>
     <col min="9" max="9" width="14.7109375" customWidth="true"/>
     <col min="10" max="10" width="13.7109375" customWidth="true"/>
     <col min="11" max="11" width="12.7109375" customWidth="true"/>
@@ -800,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="0">
-        <v>0</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D20" s="0">
         <v>0</v>
@@ -818,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>0</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J20" s="0">
         <v>0</v>
@@ -838,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="0">
-        <v>0</v>
+        <v>0.0012680860776829556</v>
       </c>
       <c r="D21" s="0">
         <v>0</v>
@@ -856,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="0">
-        <v>0</v>
+        <v>0.0019860578737264439</v>
       </c>
       <c r="J21" s="0">
         <v>0</v>
@@ -865,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>0</v>
+        <v>0.0031101296924081795</v>
       </c>
     </row>
     <row r="22">
@@ -876,13 +877,13 @@
         <v>0</v>
       </c>
       <c r="C22" s="0">
-        <v>0</v>
+        <v>0.0076085164660977117</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>0.0072127521457937566</v>
       </c>
       <c r="E22" s="0">
-        <v>0</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F22" s="0">
         <v>0</v>
@@ -894,2851 +895,2851 @@
         <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>0</v>
+        <v>0.0059581736211793161</v>
       </c>
       <c r="J22" s="0">
-        <v>0</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K22" s="0">
         <v>0</v>
       </c>
       <c r="L22" s="0">
-        <v>0</v>
+        <v>0.007775324231020426</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B23" s="0">
         <v>0</v>
       </c>
       <c r="C23" s="0">
-        <v>0</v>
+        <v>0.044383012718903318</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>0.026446757867910439</v>
       </c>
       <c r="E23" s="0">
-        <v>0</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F23" s="0">
-        <v>0</v>
+        <v>0.0072772259214787249</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H23" s="0">
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>0</v>
+        <v>0.03972115747452877</v>
       </c>
       <c r="J23" s="0">
-        <v>0</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K23" s="0">
         <v>0</v>
       </c>
       <c r="L23" s="0">
-        <v>0</v>
+        <v>0.027991167231673539</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0</v>
+        <v>0.0049227133996258832</v>
       </c>
       <c r="B24" s="0">
-        <v>0</v>
+        <v>0.087719298245614197</v>
       </c>
       <c r="C24" s="0">
-        <v>0</v>
+        <v>0.10144688621463643</v>
       </c>
       <c r="D24" s="0">
-        <v>0</v>
+        <v>0.060106267881614807</v>
       </c>
       <c r="E24" s="0">
-        <v>0.00059667651182911303</v>
+        <v>0.001790029535487339</v>
       </c>
       <c r="F24" s="0">
-        <v>0</v>
+        <v>0.032747516646654359</v>
       </c>
       <c r="G24" s="0">
-        <v>0</v>
+        <v>0.060350030175015203</v>
       </c>
       <c r="H24" s="0">
         <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>0</v>
+        <v>0.073484141327878436</v>
       </c>
       <c r="J24" s="0">
-        <v>0</v>
+        <v>0.018402649981597383</v>
       </c>
       <c r="K24" s="0">
-        <v>0</v>
+        <v>0.25773195876288707</v>
       </c>
       <c r="L24" s="0">
-        <v>0</v>
+        <v>0.069977918079184034</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0</v>
+        <v>0.044304420596632824</v>
       </c>
       <c r="B25" s="0">
-        <v>0</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C25" s="0">
-        <v>0</v>
+        <v>0.26502999023573698</v>
       </c>
       <c r="D25" s="0">
-        <v>0</v>
+        <v>0.16829755006852099</v>
       </c>
       <c r="E25" s="0">
-        <v>0</v>
+        <v>0.011336853724753116</v>
       </c>
       <c r="F25" s="0">
-        <v>0</v>
+        <v>0.092784630498853757</v>
       </c>
       <c r="G25" s="0">
-        <v>0</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H25" s="0">
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.16087068777184152</v>
       </c>
       <c r="J25" s="0">
-        <v>0</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K25" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L25" s="0">
-        <v>0</v>
+        <v>0.15239635492800038</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0</v>
+        <v>0.051688490696071628</v>
       </c>
       <c r="B26" s="0">
-        <v>0</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C26" s="0">
-        <v>0</v>
+        <v>0.54908127163671827</v>
       </c>
       <c r="D26" s="0">
-        <v>0</v>
+        <v>0.31255259298439614</v>
       </c>
       <c r="E26" s="0">
-        <v>0.003580059070974668</v>
+        <v>0.036397267221575789</v>
       </c>
       <c r="F26" s="0">
-        <v>0</v>
+        <v>0.18193064803696812</v>
       </c>
       <c r="G26" s="0">
-        <v>0</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H26" s="0">
-        <v>0</v>
+        <v>0.022723399420553292</v>
       </c>
       <c r="I26" s="0">
-        <v>0.0079442314949057548</v>
+        <v>0.39323945899783486</v>
       </c>
       <c r="J26" s="0">
-        <v>0</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K26" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L26" s="0">
-        <v>0.0062202593848163417</v>
+        <v>0.38565608185861317</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0</v>
+        <v>0.18460175248597011</v>
       </c>
       <c r="B27" s="0">
-        <v>0</v>
+        <v>1.3157894736842093</v>
       </c>
       <c r="C27" s="0">
-        <v>0.0050723443107318078</v>
+        <v>1.003056087447215</v>
       </c>
       <c r="D27" s="0">
-        <v>0.002404250715264586</v>
+        <v>0.65636044526723192</v>
       </c>
       <c r="E27" s="0">
-        <v>0.0065634416301202248</v>
+        <v>0.092484859333512248</v>
       </c>
       <c r="F27" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.35112615071134851</v>
       </c>
       <c r="G27" s="0">
-        <v>0</v>
+        <v>0.56326694830014024</v>
       </c>
       <c r="H27" s="0">
-        <v>0</v>
+        <v>0.096574447537351504</v>
       </c>
       <c r="I27" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.71895295028897077</v>
       </c>
       <c r="J27" s="0">
-        <v>0</v>
+        <v>0.64409274935590677</v>
       </c>
       <c r="K27" s="0">
-        <v>0</v>
+        <v>1.6752577319587614</v>
       </c>
       <c r="L27" s="0">
-        <v>0.0093303890772245112</v>
+        <v>0.73554567225453238</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.38643300187063073</v>
       </c>
       <c r="B28" s="0">
-        <v>0</v>
+        <v>1.9298245614035072</v>
       </c>
       <c r="C28" s="0">
-        <v>0.0050723443107318078</v>
+        <v>1.6180778351234468</v>
       </c>
       <c r="D28" s="0">
-        <v>0</v>
+        <v>1.3487846512634325</v>
       </c>
       <c r="E28" s="0">
-        <v>0.016706942331215117</v>
+        <v>0.18079298308422073</v>
       </c>
       <c r="F28" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.72044536622639377</v>
       </c>
       <c r="G28" s="0">
-        <v>0.040233353450010022</v>
+        <v>1.1064172198752757</v>
       </c>
       <c r="H28" s="0">
-        <v>0.017042549565414972</v>
+        <v>0.15338294608873473</v>
       </c>
       <c r="I28" s="0">
-        <v>0.035749041727075895</v>
+        <v>1.281007328553553</v>
       </c>
       <c r="J28" s="0">
-        <v>0</v>
+        <v>1.0489510489510481</v>
       </c>
       <c r="K28" s="0">
-        <v>0</v>
+        <v>2.4484536082474207</v>
       </c>
       <c r="L28" s="0">
-        <v>0.027991167231673539</v>
+        <v>1.2160607097315947</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.01722949689869064</v>
+        <v>0.75317515014276215</v>
       </c>
       <c r="B29" s="0">
-        <v>0</v>
+        <v>4.2982456140351078</v>
       </c>
       <c r="C29" s="0">
-        <v>0.015217032932195507</v>
+        <v>2.4474061299281109</v>
       </c>
       <c r="D29" s="0">
-        <v>0.004808501430529198</v>
+        <v>2.1181448801481118</v>
       </c>
       <c r="E29" s="0">
-        <v>0.057877621647424125</v>
+        <v>0.37292281989319665</v>
       </c>
       <c r="F29" s="0">
-        <v>0.0054579194411090749</v>
+        <v>1.2152967288869538</v>
       </c>
       <c r="G29" s="0">
-        <v>0.060350030175015369</v>
+        <v>1.7300341983504404</v>
       </c>
       <c r="H29" s="0">
-        <v>0.051127648696245198</v>
+        <v>0.38629779014940813</v>
       </c>
       <c r="I29" s="0">
-        <v>0.081428372822784437</v>
+        <v>2.0118766260848937</v>
       </c>
       <c r="J29" s="0">
-        <v>0</v>
+        <v>1.4722119985277948</v>
       </c>
       <c r="K29" s="0">
-        <v>0</v>
+        <v>6.7010309278350828</v>
       </c>
       <c r="L29" s="0">
-        <v>0.057537399309551478</v>
+        <v>1.9111746959848313</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.054149847395884562</v>
+        <v>1.3045190509008555</v>
       </c>
       <c r="B30" s="0">
-        <v>0</v>
+        <v>5.7894736842105212</v>
       </c>
       <c r="C30" s="0">
-        <v>0.062136217806464646</v>
+        <v>3.2780025108104307</v>
       </c>
       <c r="D30" s="0">
-        <v>0.024042507152645855</v>
+        <v>3.4404827735436223</v>
       </c>
       <c r="E30" s="0">
-        <v>0.12589874399594247</v>
+        <v>0.67185775231957934</v>
       </c>
       <c r="F30" s="0">
-        <v>0.018193064803696816</v>
+        <v>1.8738856747807717</v>
       </c>
       <c r="G30" s="0">
-        <v>0.12070006035003007</v>
+        <v>2.5749346208006414</v>
       </c>
       <c r="H30" s="0">
-        <v>0.13634039652331978</v>
+        <v>0.69874453218201382</v>
       </c>
       <c r="I30" s="0">
-        <v>0.17675915076165302</v>
+        <v>2.8480069909237131</v>
       </c>
       <c r="J30" s="0">
-        <v>0</v>
+        <v>2.4107471475892508</v>
       </c>
       <c r="K30" s="0">
-        <v>0.25773195876288635</v>
+        <v>7.3453608247422615</v>
       </c>
       <c r="L30" s="0">
-        <v>0.15861661431281671</v>
+        <v>2.6576058221627816</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.08122477109382685</v>
+        <v>1.8829378753568953</v>
       </c>
       <c r="B31" s="0">
-        <v>0</v>
+        <v>5.7017543859649065</v>
       </c>
       <c r="C31" s="0">
-        <v>0.15343841539963721</v>
+        <v>3.874002967321418</v>
       </c>
       <c r="D31" s="0">
-        <v>0.045680763590027124</v>
+        <v>4.5079700911210985</v>
       </c>
       <c r="E31" s="0">
-        <v>0.26074763566932163</v>
+        <v>1.1879829350517606</v>
       </c>
       <c r="F31" s="0">
-        <v>0.078230178655896293</v>
+        <v>2.6598260743004745</v>
       </c>
       <c r="G31" s="0">
-        <v>0.14081673707503506</v>
+        <v>3.9428686381009825</v>
       </c>
       <c r="H31" s="0">
-        <v>0.3351701414531611</v>
+        <v>1.334999715957506</v>
       </c>
       <c r="I31" s="0">
-        <v>0.42501638497745792</v>
+        <v>3.6920815872574497</v>
       </c>
       <c r="J31" s="0">
-        <v>0.11041589988958402</v>
+        <v>3.3676849466323118</v>
       </c>
       <c r="K31" s="0">
-        <v>0.38659793814432958</v>
+        <v>10.180412371134011</v>
       </c>
       <c r="L31" s="0">
-        <v>0.32034335831804162</v>
+        <v>3.4351382452648243</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.18460175248597011</v>
+        <v>2.6582652357979693</v>
       </c>
       <c r="B32" s="0">
-        <v>0</v>
+        <v>7.1929824561403448</v>
       </c>
       <c r="C32" s="0">
-        <v>0.33097046627525045</v>
+        <v>4.4027948617152095</v>
       </c>
       <c r="D32" s="0">
-        <v>0.12021253576322928</v>
+        <v>5.4071598586300525</v>
       </c>
       <c r="E32" s="0">
-        <v>0.53700886064620024</v>
+        <v>1.7625824159431946</v>
       </c>
       <c r="F32" s="0">
-        <v>0.13280937306698673</v>
+        <v>3.3366080849979958</v>
       </c>
       <c r="G32" s="0">
-        <v>0.72420036210018035</v>
+        <v>4.0836853751760174</v>
       </c>
       <c r="H32" s="0">
-        <v>0.53399988638300244</v>
+        <v>2.0053399988638283</v>
       </c>
       <c r="I32" s="0">
-        <v>0.80435343885920763</v>
+        <v>4.3514528013346272</v>
       </c>
       <c r="J32" s="0">
-        <v>0.18402649981597335</v>
+        <v>4.6926757453073202</v>
       </c>
       <c r="K32" s="0">
-        <v>0.64432989690721587</v>
+        <v>8.8917525773195809</v>
       </c>
       <c r="L32" s="0">
-        <v>0.67645320809877718</v>
+        <v>3.9343140608963356</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.39381707197006954</v>
+        <v>3.2711430540513904</v>
       </c>
       <c r="B33" s="0">
-        <v>0.17543859649122792</v>
+        <v>7.5438596491228003</v>
       </c>
       <c r="C33" s="0">
-        <v>0.69364308449257472</v>
+        <v>4.6348546139311892</v>
       </c>
       <c r="D33" s="0">
-        <v>0.26927608010963361</v>
+        <v>5.7341379559060366</v>
       </c>
       <c r="E33" s="0">
-        <v>0.92484859333512259</v>
+        <v>2.4475670515230146</v>
       </c>
       <c r="F33" s="0">
-        <v>0.28926973037877934</v>
+        <v>3.9206054651966635</v>
       </c>
       <c r="G33" s="0">
-        <v>1.0058338362502506</v>
+        <v>4.8682357674512131</v>
       </c>
       <c r="H33" s="0">
-        <v>1.2327444185650163</v>
+        <v>3.1471908197466312</v>
       </c>
       <c r="I33" s="0">
-        <v>1.3366169490178932</v>
+        <v>4.7605807233222732</v>
       </c>
       <c r="J33" s="0">
-        <v>0.55207949944792001</v>
+        <v>4.5454545454545414</v>
       </c>
       <c r="K33" s="0">
-        <v>1.1597938144329887</v>
+        <v>10.567010309278341</v>
       </c>
       <c r="L33" s="0">
-        <v>1.1865144776537171</v>
+        <v>4.3059745591391128</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.82455449443733309</v>
+        <v>3.7117259033179058</v>
       </c>
       <c r="B34" s="0">
-        <v>0.52631578947368374</v>
+        <v>4.9122807017543817</v>
       </c>
       <c r="C34" s="0">
-        <v>1.2503328725953906</v>
+        <v>4.5524290188817975</v>
       </c>
       <c r="D34" s="0">
-        <v>0.56499891808717762</v>
+        <v>5.707691198038126</v>
       </c>
       <c r="E34" s="0">
-        <v>1.4708076016587595</v>
+        <v>3.070497329872607</v>
       </c>
       <c r="F34" s="0">
-        <v>0.61674489684532197</v>
+        <v>4.333588036240581</v>
       </c>
       <c r="G34" s="0">
-        <v>1.4081673707503508</v>
+        <v>4.4659022329511124</v>
       </c>
       <c r="H34" s="0">
-        <v>1.9258081008918917</v>
+        <v>3.6073396580128358</v>
       </c>
       <c r="I34" s="0">
-        <v>2.162817024488092</v>
+        <v>4.9869913209270873</v>
       </c>
       <c r="J34" s="0">
-        <v>0.95693779904306131</v>
+        <v>5.3551711446448245</v>
       </c>
       <c r="K34" s="0">
-        <v>3.0927835051546366</v>
+        <v>10.567010309278341</v>
       </c>
       <c r="L34" s="0">
-        <v>1.8862936584455554</v>
+        <v>4.2981992349080915</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>1.5137343703849633</v>
+        <v>3.9578615732992208</v>
       </c>
       <c r="B35" s="0">
-        <v>0.78947368421052999</v>
+        <v>5.6140350877193246</v>
       </c>
       <c r="C35" s="0">
-        <v>1.9325631823888296</v>
+        <v>4.4040629477929167</v>
       </c>
       <c r="D35" s="0">
-        <v>1.1468275911812138</v>
+        <v>5.2172240521241804</v>
       </c>
       <c r="E35" s="0">
-        <v>2.0943345565201921</v>
+        <v>3.5520152749187197</v>
       </c>
       <c r="F35" s="0">
-        <v>1.0697522104573787</v>
+        <v>4.180766291889551</v>
       </c>
       <c r="G35" s="0">
-        <v>2.5548179440756504</v>
+        <v>4.7676523838262135</v>
       </c>
       <c r="H35" s="0">
-        <v>2.7722547293075173</v>
+        <v>4.3515309890359806</v>
       </c>
       <c r="I35" s="0">
-        <v>3.1757065400885933</v>
+        <v>4.8618696748823487</v>
       </c>
       <c r="J35" s="0">
-        <v>1.3986013986014052</v>
+        <v>5.1895472948104775</v>
       </c>
       <c r="K35" s="0">
-        <v>5.7989690721649758</v>
+        <v>8.3762886597938522</v>
       </c>
       <c r="L35" s="0">
-        <v>2.6405001088545514</v>
+        <v>4.1815693714428086</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>2.0576942010436134</v>
+        <v>3.9160185094023787</v>
       </c>
       <c r="B36" s="0">
-        <v>1.8421052631578929</v>
+        <v>4.5614035087719263</v>
       </c>
       <c r="C36" s="0">
-        <v>2.6832701403771262</v>
+        <v>4.1694670234215456</v>
       </c>
       <c r="D36" s="0">
-        <v>1.9161878200658746</v>
+        <v>4.5993316183011519</v>
       </c>
       <c r="E36" s="0">
-        <v>2.7870759867537789</v>
+        <v>3.8521435603687428</v>
       </c>
       <c r="F36" s="0">
-        <v>1.7156060109886095</v>
+        <v>4.1880435178110069</v>
       </c>
       <c r="G36" s="0">
-        <v>3.4198350432508522</v>
+        <v>3.8825186079259675</v>
       </c>
       <c r="H36" s="0">
-        <v>3.630063057433389</v>
+        <v>4.3856160881667856</v>
       </c>
       <c r="I36" s="0">
-        <v>3.8589104486504704</v>
+        <v>4.5858076304343465</v>
       </c>
       <c r="J36" s="0">
-        <v>2.1715126978284855</v>
+        <v>4.0853882959146084</v>
       </c>
       <c r="K36" s="0">
-        <v>7.2164948453608178</v>
+        <v>6.4432989690721589</v>
       </c>
       <c r="L36" s="0">
-        <v>3.2920722794140489</v>
+        <v>3.8394551052778865</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>2.6434970955990917</v>
+        <v>3.7191099734173445</v>
       </c>
       <c r="B37" s="0">
-        <v>1.4912280701754372</v>
+        <v>2.9824561403508745</v>
       </c>
       <c r="C37" s="0">
-        <v>3.5620537922114117</v>
+        <v>3.8701987090883696</v>
       </c>
       <c r="D37" s="0">
-        <v>3.1688024427187238</v>
+        <v>3.8540138965691306</v>
       </c>
       <c r="E37" s="0">
-        <v>3.3258748769354667</v>
+        <v>3.9523852143560334</v>
       </c>
       <c r="F37" s="0">
-        <v>2.4469672160972213</v>
+        <v>3.977003966088124</v>
       </c>
       <c r="G37" s="0">
-        <v>4.1038020519010221</v>
+        <v>3.3594850130758371</v>
       </c>
       <c r="H37" s="0">
-        <v>4.2947224904845731</v>
+        <v>4.6355734817928722</v>
       </c>
       <c r="I37" s="0">
-        <v>4.4666441580107605</v>
+        <v>4.1647633612043418</v>
       </c>
       <c r="J37" s="0">
-        <v>3.7909458962090508</v>
+        <v>3.1468531468531444</v>
       </c>
       <c r="K37" s="0">
-        <v>9.7938144329896826</v>
+        <v>3.9948453608247383</v>
       </c>
       <c r="L37" s="0">
-        <v>3.8767766615867845</v>
+        <v>3.7990234192765802</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>3.290833907649894</v>
+        <v>3.5369695776311874</v>
       </c>
       <c r="B38" s="0">
-        <v>4.2982456140350838</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C38" s="0">
-        <v>4.1821478841983755</v>
+        <v>3.6964709164458052</v>
       </c>
       <c r="D38" s="0">
-        <v>4.2338855095809356</v>
+        <v>3.1760151948645175</v>
       </c>
       <c r="E38" s="0">
-        <v>3.7125212566007302</v>
+        <v>3.817536322682654</v>
       </c>
       <c r="F38" s="0">
-        <v>3.2165338572935971</v>
+        <v>3.7204817523559983</v>
       </c>
       <c r="G38" s="0">
-        <v>4.6268356467511529</v>
+        <v>2.8163347415007016</v>
       </c>
       <c r="H38" s="0">
-        <v>4.4367437368630309</v>
+        <v>3.6698290064193571</v>
       </c>
       <c r="I38" s="0">
-        <v>4.871799964250954</v>
+        <v>4.1349724930984451</v>
       </c>
       <c r="J38" s="0">
-        <v>3.7173352962826613</v>
+        <v>3.1468531468531444</v>
       </c>
       <c r="K38" s="0">
-        <v>9.2783505154639094</v>
+        <v>3.479381443298966</v>
       </c>
       <c r="L38" s="0">
-        <v>4.3401859857556024</v>
+        <v>3.6559574534258048</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>3.8151028847100492</v>
+        <v>3.2760657674510161</v>
       </c>
       <c r="B39" s="0">
-        <v>6.3157894736842053</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C39" s="0">
-        <v>4.3875778287830141</v>
+        <v>3.5696623086775099</v>
       </c>
       <c r="D39" s="0">
-        <v>5.2556920635683841</v>
+        <v>2.8225903397206236</v>
       </c>
       <c r="E39" s="0">
-        <v>3.9201646827172616</v>
+        <v>3.7244547868373128</v>
       </c>
       <c r="F39" s="0">
-        <v>3.7696030273259802</v>
+        <v>3.5276352654368122</v>
       </c>
       <c r="G39" s="0">
-        <v>4.7877690605511924</v>
+        <v>2.5347012673506315</v>
       </c>
       <c r="H39" s="0">
-        <v>4.3799352383116474</v>
+        <v>3.2948929159802276</v>
       </c>
       <c r="I39" s="0">
-        <v>5.090266330360862</v>
+        <v>3.753649381342969</v>
       </c>
       <c r="J39" s="0">
-        <v>4.6742730953257228</v>
+        <v>2.5579683474420296</v>
       </c>
       <c r="K39" s="0">
-        <v>10.95360824742267</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L39" s="0">
-        <v>4.3572916990638477</v>
+        <v>3.4817901906509472</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>4.1449246824849819</v>
+        <v>3.3720586787437208</v>
       </c>
       <c r="B40" s="0">
-        <v>6.3157894736842053</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C40" s="0">
-        <v>4.6741652823393611</v>
+        <v>3.3325302121507976</v>
       </c>
       <c r="D40" s="0">
-        <v>5.8928185031134994</v>
+        <v>3.0461856562402301</v>
       </c>
       <c r="E40" s="0">
-        <v>3.8676571496762997</v>
+        <v>3.6158596616844147</v>
       </c>
       <c r="F40" s="0">
-        <v>4.2935632936724479</v>
+        <v>3.3311501655568869</v>
       </c>
       <c r="G40" s="0">
-        <v>4.5866022933011426</v>
+        <v>2.7358680346006819</v>
       </c>
       <c r="H40" s="0">
-        <v>3.9538714991762731</v>
+        <v>2.8063398284383316</v>
       </c>
       <c r="I40" s="0">
-        <v>4.7367480288375559</v>
+        <v>3.5927786935711272</v>
       </c>
       <c r="J40" s="0">
-        <v>5.4287817445712134</v>
+        <v>2.3003312476996665</v>
       </c>
       <c r="K40" s="0">
-        <v>11.082474226804113</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L40" s="0">
-        <v>3.9965166547444997</v>
+        <v>3.3325039654153548</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.6920350497194225</v>
+        <v>3.3105247612484154</v>
       </c>
       <c r="B41" s="0">
-        <v>7.8947368421052992</v>
+        <v>0.78947368421052999</v>
       </c>
       <c r="C41" s="0">
-        <v>4.5105821783182849</v>
+        <v>3.0713044801481266</v>
       </c>
       <c r="D41" s="0">
-        <v>5.6860529416007761</v>
+        <v>2.9716538840670443</v>
       </c>
       <c r="E41" s="0">
-        <v>3.7715922312718337</v>
+        <v>3.4822041230347129</v>
       </c>
       <c r="F41" s="0">
-        <v>4.4081796019357622</v>
+        <v>3.191063566568439</v>
       </c>
       <c r="G41" s="0">
-        <v>3.8422852544759785</v>
+        <v>2.7761013880507068</v>
       </c>
       <c r="H41" s="0">
-        <v>3.4425950122138431</v>
+        <v>2.4825313866954613</v>
       </c>
       <c r="I41" s="0">
-        <v>4.5619749359496549</v>
+        <v>3.3326051121129825</v>
       </c>
       <c r="J41" s="0">
-        <v>4.8951048951049181</v>
+        <v>2.6867868973132256</v>
       </c>
       <c r="K41" s="0">
-        <v>8.1185567010309665</v>
+        <v>0.25773195876288779</v>
       </c>
       <c r="L41" s="0">
-        <v>3.954529903897011</v>
+        <v>3.2423102043355363</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>3.5985034951265105</v>
+        <v>3.199763709756815</v>
       </c>
       <c r="B42" s="0">
-        <v>7.2807017543859587</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C42" s="0">
-        <v>4.3495352464525254</v>
+        <v>2.9990235737201814</v>
       </c>
       <c r="D42" s="0">
-        <v>5.4792873800879907</v>
+        <v>3.4645252806962681</v>
       </c>
       <c r="E42" s="0">
-        <v>3.7501118768459643</v>
+        <v>3.3598854381097261</v>
       </c>
       <c r="F42" s="0">
-        <v>4.3026598260742963</v>
+        <v>3.0255066768547803</v>
       </c>
       <c r="G42" s="0">
-        <v>3.3796016898008419</v>
+        <v>2.8968014484007214</v>
       </c>
       <c r="H42" s="0">
-        <v>3.0449355223541414</v>
+        <v>2.4427654377094794</v>
       </c>
       <c r="I42" s="0">
-        <v>4.1647633612043418</v>
+        <v>3.2134416396893779</v>
       </c>
       <c r="J42" s="0">
-        <v>4.3246227456753736</v>
+        <v>2.6867868973132105</v>
       </c>
       <c r="K42" s="0">
-        <v>6.5721649484536027</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L42" s="0">
-        <v>3.7865829005069478</v>
+        <v>3.0790283954840887</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3.5148173673328706</v>
+        <v>3.2194545633553187</v>
       </c>
       <c r="B43" s="0">
-        <v>4.5614035087719262</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C43" s="0">
-        <v>4.1288882689356914</v>
+        <v>2.8595341051750567</v>
       </c>
       <c r="D43" s="0">
-        <v>4.7411824105017635</v>
+        <v>3.5895463178900262</v>
       </c>
       <c r="E43" s="0">
-        <v>3.4983143888540793</v>
+        <v>3.2936543452966944</v>
       </c>
       <c r="F43" s="0">
-        <v>4.0261252410581054</v>
+        <v>2.9418185787577751</v>
       </c>
       <c r="G43" s="0">
-        <v>2.7761013880506913</v>
+        <v>3.1583182458257868</v>
       </c>
       <c r="H43" s="0">
-        <v>2.3745952394478196</v>
+        <v>2.6927228313355656</v>
       </c>
       <c r="I43" s="0">
-        <v>3.9701296895791507</v>
+        <v>2.9274493058727704</v>
       </c>
       <c r="J43" s="0">
-        <v>3.4596981965402991</v>
+        <v>2.9628266470371707</v>
       </c>
       <c r="K43" s="0">
-        <v>4.3814432989690681</v>
+        <v>0</v>
       </c>
       <c r="L43" s="0">
-        <v>3.6435169346561724</v>
+        <v>2.8582091873231086</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>3.3769813921433465</v>
+        <v>3.0151619572708448</v>
       </c>
       <c r="B44" s="0">
-        <v>4.9999999999999956</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C44" s="0">
-        <v>3.783968855805929</v>
+        <v>2.7403340138728591</v>
       </c>
       <c r="D44" s="0">
-        <v>3.9213329165965392</v>
+        <v>3.3539297477940973</v>
       </c>
       <c r="E44" s="0">
-        <v>3.3986694113786178</v>
+        <v>3.0764640949908979</v>
       </c>
       <c r="F44" s="0">
-        <v>3.7877960921296769</v>
+        <v>2.7289597205545224</v>
       </c>
       <c r="G44" s="0">
-        <v>2.7962180647756965</v>
+        <v>3.1583182458257868</v>
       </c>
       <c r="H44" s="0">
-        <v>2.5279781855365542</v>
+        <v>2.7779355791626403</v>
       </c>
       <c r="I44" s="0">
-        <v>3.7735099600802333</v>
+        <v>2.7566483287322967</v>
       </c>
       <c r="J44" s="0">
-        <v>3.2572690467427279</v>
+        <v>2.8156054471843919</v>
       </c>
       <c r="K44" s="0">
-        <v>3.2216494845360795</v>
+        <v>0</v>
       </c>
       <c r="L44" s="0">
-        <v>3.5206668118060493</v>
+        <v>2.6016234876994351</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>3.4729743034360512</v>
+        <v>2.7345672934921703</v>
       </c>
       <c r="B45" s="0">
-        <v>3.5964912280701724</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C45" s="0">
-        <v>3.7370496709316594</v>
+        <v>2.4930572287246839</v>
       </c>
       <c r="D45" s="0">
-        <v>3.195249200586634</v>
+        <v>3.1688024427187238</v>
       </c>
       <c r="E45" s="0">
-        <v>3.3921059697484979</v>
+        <v>3.0042662370595754</v>
       </c>
       <c r="F45" s="0">
-        <v>3.6276971218571448</v>
+        <v>2.550667685478293</v>
       </c>
       <c r="G45" s="0">
-        <v>2.9571514785757369</v>
+        <v>2.7761013880506913</v>
       </c>
       <c r="H45" s="0">
-        <v>2.5507015849571073</v>
+        <v>2.9938078736578966</v>
       </c>
       <c r="I45" s="0">
-        <v>3.5768902305813159</v>
+        <v>2.6513872614247958</v>
       </c>
       <c r="J45" s="0">
-        <v>2.649981597350016</v>
+        <v>3.4965034965034936</v>
       </c>
       <c r="K45" s="0">
-        <v>1.6752577319587614</v>
+        <v>0</v>
       </c>
       <c r="L45" s="0">
-        <v>3.3978166889559263</v>
+        <v>2.6731564706248228</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>3.2809884808506418</v>
+        <v>2.6410357388992791</v>
       </c>
       <c r="B46" s="0">
-        <v>3.2456140350877161</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C46" s="0">
-        <v>3.4491941312976291</v>
+        <v>2.3320102968589489</v>
       </c>
       <c r="D46" s="0">
-        <v>2.8177818382900943</v>
+        <v>2.8682711033106507</v>
       </c>
       <c r="E46" s="0">
-        <v>3.2417434887675616</v>
+        <v>2.8777708165518039</v>
       </c>
       <c r="F46" s="0">
-        <v>3.3584397627624321</v>
+        <v>2.5615835243605112</v>
       </c>
       <c r="G46" s="0">
-        <v>2.7157513578756767</v>
+        <v>2.7962180647756965</v>
       </c>
       <c r="H46" s="0">
-        <v>2.8858717264102687</v>
+        <v>3.2324035675737064</v>
       </c>
       <c r="I46" s="0">
-        <v>3.3345911699866906</v>
+        <v>2.5163353260113977</v>
       </c>
       <c r="J46" s="0">
-        <v>2.4107471475892508</v>
+        <v>2.3371365476628614</v>
       </c>
       <c r="K46" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L46" s="0">
-        <v>3.2096538425652321</v>
+        <v>2.4383416788480061</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>3.0520823077680559</v>
+        <v>2.6656493058974231</v>
       </c>
       <c r="B47" s="0">
-        <v>1.3157894736842166</v>
+        <v>1.0526315789473733</v>
       </c>
       <c r="C47" s="0">
-        <v>3.2323514120138626</v>
+        <v>2.2445123574988375</v>
       </c>
       <c r="D47" s="0">
-        <v>2.978866636212838</v>
+        <v>2.2744211766403106</v>
       </c>
       <c r="E47" s="0">
-        <v>3.0412601807929973</v>
+        <v>2.9034279065604718</v>
       </c>
       <c r="F47" s="0">
-        <v>3.1983407924899181</v>
+        <v>2.2923261652658113</v>
       </c>
       <c r="G47" s="0">
-        <v>2.6554013277006763</v>
+        <v>2.0116676725005123</v>
       </c>
       <c r="H47" s="0">
-        <v>2.8517866272794543</v>
+        <v>2.7381696301766874</v>
       </c>
       <c r="I47" s="0">
-        <v>3.0188079680642033</v>
+        <v>2.3634088697344753</v>
       </c>
       <c r="J47" s="0">
         <v>2.3371365476628743</v>
       </c>
       <c r="K47" s="0">
-        <v>0.25773195876288779</v>
+        <v>0</v>
       </c>
       <c r="L47" s="0">
-        <v>2.9312972350947173</v>
+        <v>2.2424035082263036</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>3.1776114994584983</v>
+        <v>2.6582652357979693</v>
       </c>
       <c r="B48" s="0">
-        <v>1.9298245614035072</v>
+        <v>1.3157894736842093</v>
       </c>
       <c r="C48" s="0">
-        <v>3.061159791526646</v>
+        <v>2.1240441801189447</v>
       </c>
       <c r="D48" s="0">
-        <v>3.087057918399728</v>
+        <v>1.933017575072727</v>
       </c>
       <c r="E48" s="0">
-        <v>2.9087979951669176</v>
+        <v>2.6241832990244314</v>
       </c>
       <c r="F48" s="0">
-        <v>2.9836626278062779</v>
+        <v>2.2541207291780356</v>
       </c>
       <c r="G48" s="0">
-        <v>3.4198350432508522</v>
+        <v>1.9513176423254861</v>
       </c>
       <c r="H48" s="0">
-        <v>3.0733397716298327</v>
+        <v>2.9597227745270667</v>
       </c>
       <c r="I48" s="0">
-        <v>2.9473098846100352</v>
+        <v>2.1926078925939883</v>
       </c>
       <c r="J48" s="0">
-        <v>2.3371365476628614</v>
+        <v>1.987486198012512</v>
       </c>
       <c r="K48" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L48" s="0">
-        <v>2.9546232077877623</v>
+        <v>2.1724255901471072</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>2.86009648518263</v>
+        <v>2.5893472482032074</v>
       </c>
       <c r="B49" s="0">
-        <v>0.87719298245613953</v>
+        <v>2.4561403508771908</v>
       </c>
       <c r="C49" s="0">
-        <v>2.8316362114660318</v>
+        <v>2.0860015977884561</v>
       </c>
       <c r="D49" s="0">
-        <v>3.2986319813430112</v>
+        <v>1.7767412785805288</v>
       </c>
       <c r="E49" s="0">
-        <v>2.834213431188279</v>
+        <v>2.5507920880694508</v>
       </c>
       <c r="F49" s="0">
-        <v>2.9490958046792537</v>
+        <v>2.0812866135429156</v>
       </c>
       <c r="G49" s="0">
-        <v>3.1180848923757769</v>
+        <v>1.669684168175416</v>
       </c>
       <c r="H49" s="0">
-        <v>3.1699142191671843</v>
+        <v>2.4825313866954475</v>
       </c>
       <c r="I49" s="0">
-        <v>2.8102718913229103</v>
+        <v>2.0515977835594112</v>
       </c>
       <c r="J49" s="0">
-        <v>2.9812292970187682</v>
+        <v>1.5642252484357733</v>
       </c>
       <c r="K49" s="0">
         <v>0</v>
       </c>
       <c r="L49" s="0">
-        <v>2.6436102385469451</v>
+        <v>2.0729014399900456</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>2.8059466377867457</v>
+        <v>2.4244363493157408</v>
       </c>
       <c r="B50" s="0">
-        <v>0.52631578947368374</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C50" s="0">
-        <v>2.8354404696990807</v>
+        <v>2.0365462407588208</v>
       </c>
       <c r="D50" s="0">
-        <v>3.6520568364869059</v>
+        <v>1.6733584978241518</v>
       </c>
       <c r="E50" s="0">
-        <v>2.7465019839493996</v>
+        <v>2.5173782034070205</v>
       </c>
       <c r="F50" s="0">
-        <v>2.7344176399956313</v>
+        <v>2.1085762107484607</v>
       </c>
       <c r="G50" s="0">
-        <v>2.9370348018507317</v>
+        <v>1.6495674914504108</v>
       </c>
       <c r="H50" s="0">
-        <v>2.7438504800318104</v>
+        <v>2.1530420950974247</v>
       </c>
       <c r="I50" s="0">
-        <v>2.5878334094655497</v>
+        <v>1.9304482532620983</v>
       </c>
       <c r="J50" s="0">
-        <v>3.1284504968715465</v>
+        <v>1.6562384983437601</v>
       </c>
       <c r="K50" s="0">
         <v>0</v>
       </c>
       <c r="L50" s="0">
-        <v>2.5083195969271896</v>
+        <v>1.9904830031412291</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.6681106625972211</v>
+        <v>2.2890617308260293</v>
       </c>
       <c r="B51" s="0">
-        <v>0.70175438596491169</v>
+        <v>4.122807017543856</v>
       </c>
       <c r="C51" s="0">
-        <v>2.5792870820071245</v>
+        <v>1.847601415184061</v>
       </c>
       <c r="D51" s="0">
-        <v>3.3827807563772723</v>
+        <v>1.7358690164210311</v>
       </c>
       <c r="E51" s="0">
-        <v>2.6444703004266215</v>
+        <v>2.4332468152391162</v>
       </c>
       <c r="F51" s="0">
-        <v>2.445147909616852</v>
+        <v>1.9321034821526017</v>
       </c>
       <c r="G51" s="0">
-        <v>2.2128344397505515</v>
+        <v>1.8306175819754562</v>
       </c>
       <c r="H51" s="0">
-        <v>2.5563824348122455</v>
+        <v>2.0905527466909031</v>
       </c>
       <c r="I51" s="0">
-        <v>2.3852555063454526</v>
+        <v>1.7298564080157282</v>
       </c>
       <c r="J51" s="0">
-        <v>2.705189547294808</v>
+        <v>1.5826278984173707</v>
       </c>
       <c r="K51" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L51" s="0">
-        <v>2.497434143003761</v>
+        <v>1.8769632693683311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>2.7887171408880551</v>
+        <v>2.2472186669292094</v>
       </c>
       <c r="B52" s="0">
-        <v>0.17543859649122792</v>
+        <v>2.368421052631577</v>
       </c>
       <c r="C52" s="0">
-        <v>2.3840018260439497</v>
+        <v>1.7639077340569862</v>
       </c>
       <c r="D52" s="0">
-        <v>3.144759935566078</v>
+        <v>1.7959752843026455</v>
       </c>
       <c r="E52" s="0">
-        <v>2.5848026492437102</v>
+        <v>2.3312151317163377</v>
       </c>
       <c r="F52" s="0">
-        <v>2.5033657169886814</v>
+        <v>1.9721282247207348</v>
       </c>
       <c r="G52" s="0">
-        <v>2.3536511768255863</v>
+        <v>2.4542345604506113</v>
       </c>
       <c r="H52" s="0">
-        <v>2.1757654945179783</v>
+        <v>1.8008294040788486</v>
       </c>
       <c r="I52" s="0">
-        <v>2.2442453973108756</v>
+        <v>1.7477309288792657</v>
       </c>
       <c r="J52" s="0">
-        <v>2.8340080971659893</v>
+        <v>1.7114464482885521</v>
       </c>
       <c r="K52" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L52" s="0">
-        <v>2.3636985662302097</v>
+        <v>1.7416726277485755</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>2.6459584522989048</v>
+        <v>2.1143054051393109</v>
       </c>
       <c r="B53" s="0">
-        <v>0.87719298245613953</v>
+        <v>3.6842105263157858</v>
       </c>
       <c r="C53" s="0">
-        <v>2.3142570917713874</v>
+        <v>1.5863756831813729</v>
       </c>
       <c r="D53" s="0">
-        <v>2.8201860890053592</v>
+        <v>1.752698771427883</v>
       </c>
       <c r="E53" s="0">
-        <v>2.4624839643187424</v>
+        <v>2.2679674214624521</v>
       </c>
       <c r="F53" s="0">
-        <v>2.3705563439216948</v>
+        <v>1.9084524979077959</v>
       </c>
       <c r="G53" s="0">
-        <v>1.8306175819754562</v>
+        <v>1.7903842285254461</v>
       </c>
       <c r="H53" s="0">
-        <v>1.9428506504573066</v>
+        <v>1.738340055672327</v>
       </c>
       <c r="I53" s="0">
-        <v>2.0337232626958732</v>
+        <v>1.5570693730015279</v>
       </c>
       <c r="J53" s="0">
-        <v>2.2819285977180694</v>
+        <v>1.5274199484725786</v>
       </c>
       <c r="K53" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L53" s="0">
-        <v>2.1630952010698827</v>
+        <v>1.6872453581314324</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>2.5376587575071357</v>
+        <v>2.1044599783400591</v>
       </c>
       <c r="B54" s="0">
-        <v>0.52631578947368374</v>
+        <v>3.1578947368421026</v>
       </c>
       <c r="C54" s="0">
-        <v>2.301576230994558</v>
+        <v>1.6256863515895443</v>
       </c>
       <c r="D54" s="0">
-        <v>2.4932079917293755</v>
+        <v>1.5940182242204202</v>
       </c>
       <c r="E54" s="0">
-        <v>2.391479459411078</v>
+        <v>2.2041230346967371</v>
       </c>
       <c r="F54" s="0">
-        <v>2.3378088272750408</v>
+        <v>1.8138485609285724</v>
       </c>
       <c r="G54" s="0">
-        <v>1.7702675518004409</v>
+        <v>2.2731844699255661</v>
       </c>
       <c r="H54" s="0">
-        <v>2.0167016985741051</v>
+        <v>2.124637845821733</v>
       </c>
       <c r="I54" s="0">
-        <v>1.9959881630950707</v>
+        <v>1.4418780163253946</v>
       </c>
       <c r="J54" s="0">
-        <v>2.6683842473316131</v>
+        <v>1.9138755980861226</v>
       </c>
       <c r="K54" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L54" s="0">
-        <v>2.1630952010698827</v>
+        <v>1.5488445868192691</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>2.3973614256177984</v>
+        <v>1.8435561681598882</v>
       </c>
       <c r="B55" s="0">
-        <v>1.0526315789473675</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C55" s="0">
-        <v>2.0619079623124801</v>
+        <v>1.5039500881319809</v>
       </c>
       <c r="D55" s="0">
-        <v>2.0820811194191311</v>
+        <v>1.4305291755824283</v>
       </c>
       <c r="E55" s="0">
-        <v>2.2506638026194077</v>
+        <v>2.1325218532772441</v>
       </c>
       <c r="F55" s="0">
-        <v>2.1922643088454659</v>
+        <v>1.6919550267438037</v>
       </c>
       <c r="G55" s="0">
-        <v>2.1323677328505313</v>
+        <v>1.9312009656004812</v>
       </c>
       <c r="H55" s="0">
-        <v>1.7894677043685721</v>
+        <v>2.124637845821733</v>
       </c>
       <c r="I55" s="0">
-        <v>1.8549780540604934</v>
+        <v>1.3683938749975162</v>
       </c>
       <c r="J55" s="0">
-        <v>1.8402649981597332</v>
+        <v>1.7482517482517468</v>
       </c>
       <c r="K55" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L55" s="0">
-        <v>1.9516063819861269</v>
+        <v>1.5115230305103709</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>2.3899773555183597</v>
+        <v>1.8435561681598882</v>
       </c>
       <c r="B56" s="0">
-        <v>1.0526315789473675</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C56" s="0">
-        <v>2.0035760027390639</v>
+        <v>1.4367415260147847</v>
       </c>
       <c r="D56" s="0">
-        <v>1.8464645493232017</v>
+        <v>1.392061164138195</v>
       </c>
       <c r="E56" s="0">
-        <v>2.1689191204988196</v>
+        <v>1.9869327843909406</v>
       </c>
       <c r="F56" s="0">
-        <v>2.0903831459447639</v>
+        <v>1.566422879598296</v>
       </c>
       <c r="G56" s="0">
-        <v>1.7099175216254261</v>
+        <v>1.4081673707503508</v>
       </c>
       <c r="H56" s="0">
-        <v>1.8860421519059236</v>
+        <v>1.9996591490086899</v>
       </c>
       <c r="I56" s="0">
-        <v>1.7576612182478983</v>
+        <v>1.2472443447002035</v>
       </c>
       <c r="J56" s="0">
-        <v>1.7850570482149415</v>
+        <v>1.7298490982701495</v>
       </c>
       <c r="K56" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L56" s="0">
-        <v>1.894068982676576</v>
+        <v>1.5037477062793505</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>2.1733779659348458</v>
+        <v>1.7894063207640236</v>
       </c>
       <c r="B57" s="0">
-        <v>1.4912280701754539</v>
+        <v>0.87719298245614929</v>
       </c>
       <c r="C57" s="0">
-        <v>1.913541891223596</v>
+        <v>1.2858392827705276</v>
       </c>
       <c r="D57" s="0">
-        <v>1.7142307599836684</v>
+        <v>1.1107638304522509</v>
       </c>
       <c r="E57" s="0">
-        <v>2.230973477729072</v>
+        <v>1.9457621050747538</v>
       </c>
       <c r="F57" s="0">
-        <v>1.9084524979078172</v>
+        <v>1.4445293454135431</v>
       </c>
       <c r="G57" s="0">
-        <v>2.0921343794005445</v>
+        <v>1.2472339569503244</v>
       </c>
       <c r="H57" s="0">
-        <v>2.0564676475600958</v>
+        <v>1.9258081008919132</v>
       </c>
       <c r="I57" s="0">
-        <v>1.7238982343945679</v>
+        <v>1.0545967309487507</v>
       </c>
       <c r="J57" s="0">
-        <v>1.472211998527803</v>
+        <v>1.5274199484725957</v>
       </c>
       <c r="K57" s="0">
-        <v>0.25773195876288924</v>
+        <v>0.51546391752577847</v>
       </c>
       <c r="L57" s="0">
-        <v>1.8100954809815752</v>
+        <v>1.3560165458899776</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>2.0700009845426783</v>
+        <v>1.7574086836664353</v>
       </c>
       <c r="B58" s="0">
-        <v>2.1929824561403488</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C58" s="0">
-        <v>1.8311162961741829</v>
+        <v>1.2769626802267326</v>
       </c>
       <c r="D58" s="0">
-        <v>1.7839540307263224</v>
+        <v>0.89918976750895496</v>
       </c>
       <c r="E58" s="0">
-        <v>2.0871744383782316</v>
+        <v>1.8658074524896311</v>
       </c>
       <c r="F58" s="0">
-        <v>1.9466579339955592</v>
+        <v>1.5373139759123808</v>
       </c>
       <c r="G58" s="0">
-        <v>1.9714343190504913</v>
+        <v>0.96560048280024058</v>
       </c>
       <c r="H58" s="0">
-        <v>1.9258081008918917</v>
+        <v>1.6928932568312205</v>
       </c>
       <c r="I58" s="0">
-        <v>1.6265813985819533</v>
+        <v>1.0486385573275596</v>
       </c>
       <c r="J58" s="0">
-        <v>1.5826278984173707</v>
+        <v>1.4722119985277868</v>
       </c>
       <c r="K58" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L58" s="0">
-        <v>1.7027960065934733</v>
+        <v>1.276708238733554</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.9518558629516574</v>
+        <v>1.5875750713793428</v>
       </c>
       <c r="B59" s="0">
-        <v>2.1052631578947349</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C59" s="0">
-        <v>1.7296694099595464</v>
+        <v>1.1691753636236817</v>
       </c>
       <c r="D59" s="0">
-        <v>1.7046137571225912</v>
+        <v>0.78859423460678413</v>
       </c>
       <c r="E59" s="0">
-        <v>1.9105581908768143</v>
+        <v>1.7888361824636758</v>
       </c>
       <c r="F59" s="0">
-        <v>1.9011752719863173</v>
+        <v>1.473638249099442</v>
       </c>
       <c r="G59" s="0">
-        <v>2.1726010863005412</v>
+        <v>1.1667672500502908</v>
       </c>
       <c r="H59" s="0">
-        <v>2.0962335965460412</v>
+        <v>1.6417656081349756</v>
       </c>
       <c r="I59" s="0">
-        <v>1.4518083056940267</v>
+        <v>1.0943178884232676</v>
       </c>
       <c r="J59" s="0">
-        <v>1.9138755980861226</v>
+        <v>1.159366948840632</v>
       </c>
       <c r="K59" s="0">
         <v>0.90206185567010222</v>
       </c>
       <c r="L59" s="0">
-        <v>1.5643952352813097</v>
+        <v>1.2487170715018805</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.9444717928522184</v>
+        <v>1.4989662301860771</v>
       </c>
       <c r="B60" s="0">
-        <v>3.7719298245614001</v>
+        <v>0</v>
       </c>
       <c r="C60" s="0">
-        <v>1.6282225237449102</v>
+        <v>1.1095753179725829</v>
       </c>
       <c r="D60" s="0">
-        <v>1.9041665664895517</v>
+        <v>0.80061548818310691</v>
       </c>
       <c r="E60" s="0">
-        <v>1.9153316029714473</v>
+        <v>1.7017214117366253</v>
       </c>
       <c r="F60" s="0">
-        <v>1.8647891423789233</v>
+        <v>1.2535021649747105</v>
       </c>
       <c r="G60" s="0">
-        <v>1.7903842285254461</v>
+        <v>1.4282840474753558</v>
       </c>
       <c r="H60" s="0">
-        <v>1.7894677043685721</v>
+        <v>1.4429358632051343</v>
       </c>
       <c r="I60" s="0">
-        <v>1.3107981966594495</v>
+        <v>1.0565827888224653</v>
       </c>
       <c r="J60" s="0">
-        <v>1.7850570482149415</v>
+        <v>1.1409642988590347</v>
       </c>
       <c r="K60" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L60" s="0">
-        <v>1.5628401704351056</v>
+        <v>1.1243118838055537</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.8115585310623199</v>
+        <v>1.3242099044993589</v>
       </c>
       <c r="B61" s="0">
-        <v>2.8070175438596467</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C61" s="0">
-        <v>1.5965203718028367</v>
+        <v>1.0195412064570935</v>
       </c>
       <c r="D61" s="0">
-        <v>1.7262520135599724</v>
+        <v>0.71887096386411109</v>
       </c>
       <c r="E61" s="0">
-        <v>1.8419403920164665</v>
+        <v>1.5794027268116575</v>
       </c>
       <c r="F61" s="0">
-        <v>1.6683040424989979</v>
+        <v>1.3062620529054314</v>
       </c>
       <c r="G61" s="0">
-        <v>1.2271172802253056</v>
+        <v>1.2070006035003007</v>
       </c>
       <c r="H61" s="0">
-        <v>1.7042549565414971</v>
+        <v>1.2668295176958462</v>
       </c>
       <c r="I61" s="0">
-        <v>1.2353279974578448</v>
+        <v>1.0208337470953894</v>
       </c>
       <c r="J61" s="0">
-        <v>1.6562384983437601</v>
+        <v>1.0673536989326453</v>
       </c>
       <c r="K61" s="0">
-        <v>0.77319587628865916</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L61" s="0">
-        <v>1.4664261499704525</v>
+        <v>1.1009859111124925</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.7451019001673707</v>
+        <v>1.2380624200059063</v>
       </c>
       <c r="B62" s="0">
-        <v>3.1578947368421026</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C62" s="0">
-        <v>1.4329372677817358</v>
+        <v>0.92697092278623794</v>
       </c>
       <c r="D62" s="0">
-        <v>1.4882311927487786</v>
+        <v>0.66116894669776105</v>
       </c>
       <c r="E62" s="0">
-        <v>1.7148482949968658</v>
+        <v>1.4928846325964365</v>
       </c>
       <c r="F62" s="0">
-        <v>1.6100862351271681</v>
+        <v>1.1661754539169658</v>
       </c>
       <c r="G62" s="0">
-        <v>1.4886340776503708</v>
+        <v>1.3075839871253259</v>
       </c>
       <c r="H62" s="0">
-        <v>1.4202124637845808</v>
+        <v>1.0566380730557283</v>
       </c>
       <c r="I62" s="0">
-        <v>1.2611467498162885</v>
+        <v>0.84804671208118931</v>
       </c>
       <c r="J62" s="0">
-        <v>1.6194331983805654</v>
+        <v>0.92013249907986661</v>
       </c>
       <c r="K62" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L62" s="0">
-        <v>1.3777874537368195</v>
+        <v>1.0698846141884109</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.6294181352761625</v>
+        <v>1.2282169932066545</v>
       </c>
       <c r="B63" s="0">
-        <v>3.2456140350877161</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C63" s="0">
-        <v>1.3872861689851494</v>
+        <v>0.90921771769867665</v>
       </c>
       <c r="D63" s="0">
-        <v>1.3271463948260513</v>
+        <v>0.69242420599620058</v>
       </c>
       <c r="E63" s="0">
-        <v>1.6193800531042082</v>
+        <v>1.3580357409230575</v>
       </c>
       <c r="F63" s="0">
-        <v>1.6028090092056895</v>
+        <v>1.1625368409562264</v>
       </c>
       <c r="G63" s="0">
-        <v>1.2271172802253056</v>
+        <v>1.0661838664252656</v>
       </c>
       <c r="H63" s="0">
-        <v>1.3463614156677828</v>
+        <v>1.4202124637845808</v>
       </c>
       <c r="I63" s="0">
-        <v>1.0645270203173711</v>
+        <v>0.81229767035411338</v>
       </c>
       <c r="J63" s="0">
-        <v>1.6746411483253574</v>
+        <v>1.1225616488774373</v>
       </c>
       <c r="K63" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>1.2720430441949417</v>
+        <v>1.0232326688022881</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.5678842177808394</v>
+        <v>1.124840011814511</v>
       </c>
       <c r="B64" s="0">
-        <v>1.7543859649122791</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C64" s="0">
-        <v>1.2985201435473428</v>
+        <v>0.85215384420294371</v>
       </c>
       <c r="D64" s="0">
-        <v>1.0097853004111259</v>
+        <v>0.69242420599620058</v>
       </c>
       <c r="E64" s="0">
-        <v>1.5823861093708032</v>
+        <v>1.3449088576628168</v>
       </c>
       <c r="F64" s="0">
-        <v>1.4954699268638783</v>
+        <v>1.0715715169377424</v>
       </c>
       <c r="G64" s="0">
-        <v>1.4685174009253659</v>
+        <v>1.0259505129752555</v>
       </c>
       <c r="H64" s="0">
-        <v>1.3974890643640276</v>
+        <v>1.2497869681304312</v>
       </c>
       <c r="I64" s="0">
-        <v>1.0804154833071826</v>
+        <v>0.77853468650076396</v>
       </c>
       <c r="J64" s="0">
-        <v>1.2697828487302161</v>
+        <v>1.0489510489510481</v>
       </c>
       <c r="K64" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>1.2564923957329008</v>
+        <v>0.95014462103069619</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.466968593088509</v>
+        <v>1.0140789603229292</v>
       </c>
       <c r="B65" s="0">
-        <v>1.4035087719298234</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C65" s="0">
-        <v>1.2262392371194146</v>
+        <v>0.78114102385269846</v>
       </c>
       <c r="D65" s="0">
-        <v>0.93525352823792385</v>
+        <v>0.57702017166350061</v>
       </c>
       <c r="E65" s="0">
-        <v>1.4153166860586519</v>
+        <v>1.2190101136668743</v>
       </c>
       <c r="F65" s="0">
-        <v>1.439071425972418</v>
+        <v>0.92784630498853748</v>
       </c>
       <c r="G65" s="0">
-        <v>1.4282840474753558</v>
+        <v>0.94548380607523552</v>
       </c>
       <c r="H65" s="0">
-        <v>1.3406805658126444</v>
+        <v>1.1532125205930797</v>
       </c>
       <c r="I65" s="0">
-        <v>0.91358662191416184</v>
+        <v>0.65738515620345117</v>
       </c>
       <c r="J65" s="0">
-        <v>1.1225616488774373</v>
+        <v>1.3065881486934106</v>
       </c>
       <c r="K65" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L65" s="0">
-        <v>1.1662986346530639</v>
+        <v>0.89105215687494088</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.393127892094121</v>
+        <v>0.9771586098257351</v>
       </c>
       <c r="B66" s="0">
-        <v>1.0526315789473675</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C66" s="0">
-        <v>1.1514221585361204</v>
+        <v>0.77733676561964959</v>
       </c>
       <c r="D66" s="0">
-        <v>0.82465799533575279</v>
+        <v>0.45921188661553586</v>
       </c>
       <c r="E66" s="0">
-        <v>1.3144783555595323</v>
+        <v>1.1533756973656721</v>
       </c>
       <c r="F66" s="0">
-        <v>1.3499254084343038</v>
+        <v>0.902376014263362</v>
       </c>
       <c r="G66" s="0">
-        <v>1.2673506336753158</v>
+        <v>0.82478374572520541</v>
       </c>
       <c r="H66" s="0">
-        <v>1.2043401692893247</v>
+        <v>1.1077657217519732</v>
       </c>
       <c r="I66" s="0">
-        <v>0.92947508490397324</v>
+        <v>0.68518996643562136</v>
       </c>
       <c r="J66" s="0">
-        <v>1.2881854987118135</v>
+        <v>1.0305483989694506</v>
       </c>
       <c r="K66" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L66" s="0">
-        <v>1.0885453923428599</v>
+        <v>0.88794202718253279</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.2577532736044097</v>
+        <v>0.96239046962685748</v>
       </c>
       <c r="B67" s="0">
-        <v>1.2280701754385954</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C67" s="0">
-        <v>1.0791412521081922</v>
+        <v>0.68857074018184294</v>
       </c>
       <c r="D67" s="0">
-        <v>0.78859423460678413</v>
+        <v>0.40872262159497952</v>
       </c>
       <c r="E67" s="0">
-        <v>1.2792744413616148</v>
+        <v>0.99704645126644509</v>
       </c>
       <c r="F67" s="0">
-        <v>1.2462249390532318</v>
+        <v>0.89146017538114386</v>
       </c>
       <c r="G67" s="0">
-        <v>1.2874673104003207</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H67" s="0">
-        <v>1.1986593194341861</v>
+        <v>1.1588933704482181</v>
       </c>
       <c r="I67" s="0">
-        <v>0.80435343885920763</v>
+        <v>0.54219379952731772</v>
       </c>
       <c r="J67" s="0">
-        <v>1.1777695988222294</v>
+        <v>0.92013249907986661</v>
       </c>
       <c r="K67" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L67" s="0">
-        <v>1.0154573445712676</v>
+        <v>0.85684073025845109</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.242985133405532</v>
+        <v>0.82455449443733309</v>
       </c>
       <c r="B68" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C68" s="0">
-        <v>0.99671565705880039</v>
+        <v>0.68983882625952586</v>
       </c>
       <c r="D68" s="0">
-        <v>0.68521145385040694</v>
+        <v>0.27168033082489818</v>
       </c>
       <c r="E68" s="0">
-        <v>1.173662698767862</v>
+        <v>0.90098153286195815</v>
       </c>
       <c r="F68" s="0">
-        <v>1.222573954808426</v>
+        <v>0.83688098097005348</v>
       </c>
       <c r="G68" s="0">
-        <v>1.0661838664252656</v>
+        <v>0.74431703882518541</v>
       </c>
       <c r="H68" s="0">
-        <v>1.0623189229108665</v>
+        <v>1.0964040220416964</v>
       </c>
       <c r="I68" s="0">
-        <v>0.76066016563722594</v>
+        <v>0.53623562590613838</v>
       </c>
       <c r="J68" s="0">
-        <v>0.73610599926389342</v>
+        <v>0.97534044902465866</v>
       </c>
       <c r="K68" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L68" s="0">
-        <v>1.0652194196497984</v>
+        <v>0.75887164494759363</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.090381018017142</v>
+        <v>0.81717042433790343</v>
       </c>
       <c r="B69" s="0">
-        <v>0.087719298245614932</v>
+        <v>0.96491228070176427</v>
       </c>
       <c r="C69" s="0">
-        <v>0.93331135317466296</v>
+        <v>0.59473237043331106</v>
       </c>
       <c r="D69" s="0">
-        <v>0.63712643954512227</v>
+        <v>0.29572283797754734</v>
       </c>
       <c r="E69" s="0">
-        <v>1.0829678689698492</v>
+        <v>0.85563411796295519</v>
       </c>
       <c r="F69" s="0">
-        <v>1.0497398391733179</v>
+        <v>0.74045773751046862</v>
       </c>
       <c r="G69" s="0">
-        <v>0.96560048280025124</v>
+        <v>0.80466706900020935</v>
       </c>
       <c r="H69" s="0">
-        <v>1.1816167698687843</v>
+        <v>1.0339146736351863</v>
       </c>
       <c r="I69" s="0">
-        <v>0.8023673809854901</v>
+        <v>0.52233322079005917</v>
       </c>
       <c r="J69" s="0">
-        <v>1.0121457489878647</v>
+        <v>0.57048214942952369</v>
       </c>
       <c r="K69" s="0">
-        <v>0.12886597938144462</v>
+        <v>0</v>
       </c>
       <c r="L69" s="0">
-        <v>1.0045718906478502</v>
+        <v>0.6609025596367436</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.0534606675199361</v>
+        <v>0.70394801614649927</v>
       </c>
       <c r="B70" s="0">
-        <v>0.17543859649122792</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C70" s="0">
-        <v>0.93331135317465264</v>
+        <v>0.55288552986976713</v>
       </c>
       <c r="D70" s="0">
-        <v>0.71646671314884647</v>
+        <v>0.2548505758180461</v>
       </c>
       <c r="E70" s="0">
-        <v>1.0077866284793691</v>
+        <v>0.79954652585100916</v>
       </c>
       <c r="F70" s="0">
-        <v>1.0843066623003301</v>
+        <v>0.73318051158898168</v>
       </c>
       <c r="G70" s="0">
-        <v>0.96560048280024058</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H70" s="0">
-        <v>1.1304891211725263</v>
+        <v>0.84076577856047185</v>
       </c>
       <c r="I70" s="0">
-        <v>0.77059045500585821</v>
+        <v>0.46076542670453374</v>
       </c>
       <c r="J70" s="0">
-        <v>1.3065881486934106</v>
+        <v>0.60728744939271206</v>
       </c>
       <c r="K70" s="0">
         <v>0</v>
       </c>
       <c r="L70" s="0">
-        <v>0.92681864833763494</v>
+        <v>0.65934749479053212</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.97223589642610919</v>
+        <v>0.65964359554986651</v>
       </c>
       <c r="B71" s="0">
-        <v>0.17543859649122792</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C71" s="0">
-        <v>0.92063049239782313</v>
+        <v>0.4894812259856195</v>
       </c>
       <c r="D71" s="0">
-        <v>0.6275094366840569</v>
+        <v>0.2548505758180461</v>
       </c>
       <c r="E71" s="0">
-        <v>0.91709179868134416</v>
+        <v>0.74644231629821822</v>
       </c>
       <c r="F71" s="0">
-        <v>1.057017065094785</v>
+        <v>0.72044536622639377</v>
       </c>
       <c r="G71" s="0">
         <v>0.64373365520016035</v>
       </c>
       <c r="H71" s="0">
-        <v>0.99414872464920667</v>
+        <v>0.82940407885019529</v>
       </c>
       <c r="I71" s="0">
-        <v>0.62163611447637523</v>
+        <v>0.4230303271037314</v>
       </c>
       <c r="J71" s="0">
-        <v>1.0121457489878534</v>
+        <v>0.47846889952153066</v>
       </c>
       <c r="K71" s="0">
         <v>0</v>
       </c>
       <c r="L71" s="0">
-        <v>0.85995085995085918</v>
+        <v>0.64690697602089953</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.88608841193265642</v>
+        <v>0.65964359554986651</v>
       </c>
       <c r="B72" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C72" s="0">
-        <v>0.74690269975525869</v>
+        <v>0.41339606132464241</v>
       </c>
       <c r="D72" s="0">
-        <v>0.63231793811458603</v>
+        <v>0.26206332796383985</v>
       </c>
       <c r="E72" s="0">
-        <v>0.82580029237149011</v>
+        <v>0.64202392672812381</v>
       </c>
       <c r="F72" s="0">
-        <v>0.90419532074373166</v>
+        <v>0.62948004220790976</v>
       </c>
       <c r="G72" s="0">
-        <v>0.74431703882518541</v>
+        <v>0.78455039227519552</v>
       </c>
       <c r="H72" s="0">
-        <v>0.86917002783616348</v>
+        <v>0.65329773334090724</v>
       </c>
       <c r="I72" s="0">
-        <v>0.5680125518857615</v>
+        <v>0.42104426923000493</v>
       </c>
       <c r="J72" s="0">
-        <v>1.2881854987118135</v>
+        <v>0.53367684946632266</v>
       </c>
       <c r="K72" s="0">
         <v>0</v>
       </c>
       <c r="L72" s="0">
-        <v>0.85217553571983873</v>
+        <v>0.58159425248032792</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.88854976863246948</v>
+        <v>0.51688490696071632</v>
       </c>
       <c r="B73" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C73" s="0">
-        <v>0.68730265410415992</v>
+        <v>0.38169390938256859</v>
       </c>
       <c r="D73" s="0">
-        <v>0.4712331401918588</v>
+        <v>0.32697809727598365</v>
       </c>
       <c r="E73" s="0">
-        <v>0.74166890420358544</v>
+        <v>0.57638951042692155</v>
       </c>
       <c r="F73" s="0">
-        <v>0.89691809482225293</v>
+        <v>0.61310628388458266</v>
       </c>
       <c r="G73" s="0">
-        <v>0.84490042245021046</v>
+        <v>0.54315027157513529</v>
       </c>
       <c r="H73" s="0">
-        <v>0.67602113276146047</v>
+        <v>0.74987218087825869</v>
       </c>
       <c r="I73" s="0">
-        <v>0.55808226251712922</v>
+        <v>0.36543464876566473</v>
       </c>
       <c r="J73" s="0">
-        <v>0.95693779904306131</v>
+        <v>0.57048214942951736</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
       </c>
       <c r="L73" s="0">
-        <v>0.74176593163934879</v>
+        <v>0.51783659378596037</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.74579108004331918</v>
+        <v>0.51442355026090336</v>
       </c>
       <c r="B74" s="0">
-        <v>0.61403508771929771</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C74" s="0">
-        <v>0.65813667431745215</v>
+        <v>0.3094130029546403</v>
       </c>
       <c r="D74" s="0">
-        <v>0.41353112302550876</v>
+        <v>0.22840381795013565</v>
       </c>
       <c r="E74" s="0">
-        <v>0.61278677764849732</v>
+        <v>0.51314180017303579</v>
       </c>
       <c r="F74" s="0">
-        <v>0.83142306152894441</v>
+        <v>0.57853946075755869</v>
       </c>
       <c r="G74" s="0">
-        <v>0.6638503319251654</v>
+        <v>0.52303359485013035</v>
       </c>
       <c r="H74" s="0">
-        <v>0.73851048116798212</v>
+        <v>0.67034028290632219</v>
       </c>
       <c r="I74" s="0">
-        <v>0.50048658417906255</v>
+        <v>0.28599233381660716</v>
       </c>
       <c r="J74" s="0">
-        <v>0.79131394920868536</v>
+        <v>0.331247699668752</v>
       </c>
       <c r="K74" s="0">
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.67023294871396077</v>
+        <v>0.50073088047771552</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.74579108004331918</v>
+        <v>0.52426897706015507</v>
       </c>
       <c r="B75" s="0">
-        <v>0.70175438596491169</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C75" s="0">
-        <v>0.62770260845306125</v>
+        <v>0.29039171178939599</v>
       </c>
       <c r="D75" s="0">
-        <v>0.35582910585915867</v>
+        <v>0.22599956723487105</v>
       </c>
       <c r="E75" s="0">
-        <v>0.63367045556251622</v>
+        <v>0.47734120946328906</v>
       </c>
       <c r="F75" s="0">
-        <v>0.80959138376450834</v>
+        <v>0.4657424589746384</v>
       </c>
       <c r="G75" s="0">
-        <v>0.82478374572520541</v>
+        <v>0.40233353450010018</v>
       </c>
       <c r="H75" s="0">
-        <v>0.73282963131284373</v>
+        <v>0.71578708174742878</v>
       </c>
       <c r="I75" s="0">
-        <v>0.44289090584099577</v>
+        <v>0.26215963933188991</v>
       </c>
       <c r="J75" s="0">
-        <v>0.60728744939271206</v>
+        <v>0.55207949944792001</v>
       </c>
       <c r="K75" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L75" s="0">
-        <v>0.70133424563804247</v>
+        <v>0.44785867570677662</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.63503002855173707</v>
+        <v>0.44304420596632821</v>
       </c>
       <c r="B76" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C76" s="0">
-        <v>0.54527701340366941</v>
+        <v>0.20796611674000412</v>
       </c>
       <c r="D76" s="0">
-        <v>0.25965907724857523</v>
+        <v>0.14906354434640432</v>
       </c>
       <c r="E76" s="0">
-        <v>0.55073242041826975</v>
+        <v>0.40812673409111217</v>
       </c>
       <c r="F76" s="0">
-        <v>0.68951715606010922</v>
+        <v>0.48211621729796561</v>
       </c>
       <c r="G76" s="0">
-        <v>0.62361697847515529</v>
+        <v>0.34198350432508523</v>
       </c>
       <c r="H76" s="0">
-        <v>0.73282963131284373</v>
+        <v>0.66465943305118391</v>
       </c>
       <c r="I76" s="0">
-        <v>0.44289090584099577</v>
+        <v>0.2919505074377865</v>
       </c>
       <c r="J76" s="0">
-        <v>0.73610599926389342</v>
+        <v>0.69930069930069871</v>
       </c>
       <c r="K76" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L76" s="0">
-        <v>0.64224178148228728</v>
+        <v>0.45563399993779702</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.58580289455547851</v>
+        <v>0.4307374224672636</v>
       </c>
       <c r="B77" s="0">
-        <v>1.3157894736842093</v>
+        <v>0</v>
       </c>
       <c r="C77" s="0">
-        <v>0.53640041085988865</v>
+        <v>0.17626396479793033</v>
       </c>
       <c r="D77" s="0">
-        <v>0.3341908494217774</v>
+        <v>0.13704229077008137</v>
       </c>
       <c r="E77" s="0">
-        <v>0.49345147528267508</v>
+        <v>0.33533219964796057</v>
       </c>
       <c r="F77" s="0">
-        <v>0.72408397918713319</v>
+        <v>0.46938107193537776</v>
       </c>
       <c r="G77" s="0">
-        <v>0.60350030175015035</v>
+        <v>0.36210018105009018</v>
       </c>
       <c r="H77" s="0">
-        <v>0.65329773334090724</v>
+        <v>0.69306368232687543</v>
       </c>
       <c r="I77" s="0">
-        <v>0.37933705388174976</v>
+        <v>0.26017358145816344</v>
       </c>
       <c r="J77" s="0">
-        <v>0.36805299963194671</v>
+        <v>0.42326094957673871</v>
       </c>
       <c r="K77" s="0">
         <v>0</v>
       </c>
       <c r="L77" s="0">
-        <v>0.61269554940440962</v>
+        <v>0.37943582247379681</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.59318696465491727</v>
+        <v>0.35443536477306259</v>
       </c>
       <c r="B78" s="0">
-        <v>1.2280701754385954</v>
+        <v>0</v>
       </c>
       <c r="C78" s="0">
-        <v>0.47426419305342404</v>
+        <v>0.1483660710889054</v>
       </c>
       <c r="D78" s="0">
-        <v>0.27408458154016274</v>
+        <v>0.1178082850479647</v>
       </c>
       <c r="E78" s="0">
-        <v>0.40335332199647927</v>
+        <v>0.30967510963930878</v>
       </c>
       <c r="F78" s="0">
-        <v>0.73318051158898168</v>
+        <v>0.41662118400465709</v>
       </c>
       <c r="G78" s="0">
-        <v>0.60350030175015035</v>
+        <v>0.20116676725005009</v>
       </c>
       <c r="H78" s="0">
-        <v>0.67602113276146047</v>
+        <v>0.49991478725217248</v>
       </c>
       <c r="I78" s="0">
-        <v>0.35550435939703251</v>
+        <v>0.1807312665091059</v>
       </c>
       <c r="J78" s="0">
-        <v>0.58888479941111471</v>
+        <v>0.38645564961354401</v>
       </c>
       <c r="K78" s="0">
         <v>0</v>
       </c>
       <c r="L78" s="0">
-        <v>0.50695113986253182</v>
+        <v>0.34522439585730691</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.5759574677562268</v>
+        <v>0.34458993797381088</v>
       </c>
       <c r="B79" s="0">
-        <v>0.78947368421052566</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C79" s="0">
-        <v>0.40578754485854462</v>
+        <v>0.083693681127074829</v>
       </c>
       <c r="D79" s="0">
-        <v>0.25244632510278148</v>
+        <v>0.10819128218690635</v>
       </c>
       <c r="E79" s="0">
-        <v>0.37471284942868194</v>
+        <v>0.28938810823711897</v>
       </c>
       <c r="F79" s="0">
-        <v>0.56944292835571031</v>
+        <v>0.36749990903467566</v>
       </c>
       <c r="G79" s="0">
-        <v>0.54315027157513529</v>
+        <v>0.30175015087507517</v>
       </c>
       <c r="H79" s="0">
-        <v>0.65329773334090724</v>
+        <v>0.40902118956995931</v>
       </c>
       <c r="I79" s="0">
-        <v>0.29393656531151291</v>
+        <v>0.19264761375146455</v>
       </c>
       <c r="J79" s="0">
-        <v>0.55207949944792001</v>
+        <v>0.49687154950312801</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.44319348116816437</v>
+        <v>0.31567816377942931</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.47750319976370936</v>
+        <v>0.30028551737717801</v>
       </c>
       <c r="B80" s="0">
-        <v>0.78947368421052566</v>
+        <v>0</v>
       </c>
       <c r="C80" s="0">
-        <v>0.35506410175122655</v>
+        <v>0.083693681127074829</v>
       </c>
       <c r="D80" s="0">
-        <v>0.25725482653331067</v>
+        <v>0.10578703147164176</v>
       </c>
       <c r="E80" s="0">
-        <v>0.3251886989468657</v>
+        <v>0.24702407589725209</v>
       </c>
       <c r="F80" s="0">
-        <v>0.5239602663464682</v>
+        <v>0.32383655350580332</v>
       </c>
       <c r="G80" s="0">
-        <v>0.5833836250251454</v>
+        <v>0.14081673707503506</v>
       </c>
       <c r="H80" s="0">
-        <v>0.57376583536897063</v>
+        <v>0.39765948985968264</v>
       </c>
       <c r="I80" s="0">
-        <v>0.27208992870052207</v>
+        <v>0.16682886139302086</v>
       </c>
       <c r="J80" s="0">
-        <v>0.5152741994847253</v>
+        <v>0.25763709974236265</v>
       </c>
       <c r="K80" s="0">
         <v>0</v>
       </c>
       <c r="L80" s="0">
-        <v>0.46651945386122556</v>
+        <v>0.26747115354710271</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.40858521216894716</v>
+        <v>0.26582652357979697</v>
       </c>
       <c r="B81" s="0">
-        <v>0.70175438596491169</v>
+        <v>0</v>
       </c>
       <c r="C81" s="0">
-        <v>0.31575343334305506</v>
+        <v>0.063404303884147598</v>
       </c>
       <c r="D81" s="0">
-        <v>0.27648883225542736</v>
+        <v>0.062510518596879228</v>
       </c>
       <c r="E81" s="0">
-        <v>0.28401801963065698</v>
+        <v>0.20764342611653075</v>
       </c>
       <c r="F81" s="0">
-        <v>0.54579194411090437</v>
+        <v>0.21831677764436178</v>
       </c>
       <c r="G81" s="0">
-        <v>0.38221685777509523</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H81" s="0">
-        <v>0.44878713855592761</v>
+        <v>0.37493609043912934</v>
       </c>
       <c r="I81" s="0">
-        <v>0.24229906059462553</v>
+        <v>0.12909376179221851</v>
       </c>
       <c r="J81" s="0">
-        <v>0.49687154950312801</v>
+        <v>0.331247699668752</v>
       </c>
       <c r="K81" s="0">
         <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>0.42142257332130711</v>
+        <v>0.24725531054644959</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.45781234616521094</v>
+        <v>0.22152210298316657</v>
       </c>
       <c r="B82" s="0">
-        <v>1.228070175438609</v>
+        <v>0</v>
       </c>
       <c r="C82" s="0">
-        <v>0.20162568635159162</v>
+        <v>0.041846840563537879</v>
       </c>
       <c r="D82" s="0">
-        <v>0.19234005722116898</v>
+        <v>0.093765777895319882</v>
       </c>
       <c r="E82" s="0">
-        <v>0.27447119544139426</v>
+        <v>0.17780960052507713</v>
       </c>
       <c r="F82" s="0">
-        <v>0.49121274969981948</v>
+        <v>0.23650984244806122</v>
       </c>
       <c r="G82" s="0">
-        <v>0.341983504325089</v>
+        <v>0.14081673707503664</v>
       </c>
       <c r="H82" s="0">
-        <v>0.38061694029427195</v>
+        <v>0.23859569391581223</v>
       </c>
       <c r="I82" s="0">
-        <v>0.24031300272090172</v>
+        <v>0.11320529880240827</v>
       </c>
       <c r="J82" s="0">
-        <v>0.55207949944792611</v>
+        <v>0.27603974972396306</v>
       </c>
       <c r="K82" s="0">
         <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>0.39032127639722974</v>
+        <v>0.18816284639069642</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.31997637097568149</v>
+        <v>0.25105838338091935</v>
       </c>
       <c r="B83" s="0">
-        <v>1.2280701754385954</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C83" s="0">
-        <v>0.23205975221598021</v>
+        <v>0.038042582330488559</v>
       </c>
       <c r="D83" s="0">
-        <v>0.1538720457769335</v>
+        <v>0.074531772173202157</v>
       </c>
       <c r="E83" s="0">
-        <v>0.23270383961335342</v>
+        <v>0.14737909842179048</v>
       </c>
       <c r="F83" s="0">
-        <v>0.42389840992613581</v>
+        <v>0.18920787395844688</v>
       </c>
       <c r="G83" s="0">
         <v>0.30175015087507517</v>
       </c>
       <c r="H83" s="0">
-        <v>0.38629779014940602</v>
+        <v>0.28404249275691618</v>
       </c>
       <c r="I83" s="0">
-        <v>0.19066155587773811</v>
+        <v>0.097316835812595495</v>
       </c>
       <c r="J83" s="0">
-        <v>0.49687154950312801</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K83" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L83" s="0">
-        <v>0.34055920131869472</v>
+        <v>0.16328180885142896</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.39135571527025664</v>
+        <v>0.16737225558727956</v>
       </c>
       <c r="B84" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C84" s="0">
-        <v>0.14963415716658834</v>
+        <v>0.022825549398293135</v>
       </c>
       <c r="D84" s="0">
-        <v>0.12021253576322928</v>
+        <v>0.064914769312143808</v>
       </c>
       <c r="E84" s="0">
-        <v>0.20525672006921428</v>
+        <v>0.11277186073570204</v>
       </c>
       <c r="F84" s="0">
-        <v>0.40752465160280865</v>
+        <v>0.16191827675290166</v>
       </c>
       <c r="G84" s="0">
-        <v>0.30175015087507517</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H84" s="0">
-        <v>0.28404249275691618</v>
+        <v>0.16474464579901138</v>
       </c>
       <c r="I84" s="0">
-        <v>0.16881491926674727</v>
+        <v>0.07149808345415179</v>
       </c>
       <c r="J84" s="0">
-        <v>0.331247699668752</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K84" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L84" s="0">
-        <v>0.30634777470220481</v>
+        <v>0.12596025254253093</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.30520823077680392</v>
+        <v>0.15998818548784075</v>
       </c>
       <c r="B85" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C85" s="0">
-        <v>0.11666391914683158</v>
+        <v>0.016485119009878375</v>
       </c>
       <c r="D85" s="0">
-        <v>0.12261678647849387</v>
+        <v>0.064914769312143808</v>
       </c>
       <c r="E85" s="0">
-        <v>0.17542289447775875</v>
+        <v>0.11277186073570204</v>
       </c>
       <c r="F85" s="0">
-        <v>0.38023505439726341</v>
+        <v>0.13826729250809577</v>
       </c>
       <c r="G85" s="0">
-        <v>0.18105009052504509</v>
+        <v>0.080466706900020044</v>
       </c>
       <c r="H85" s="0">
-        <v>0.26699994319150122</v>
+        <v>0.27836164290177784</v>
       </c>
       <c r="I85" s="0">
-        <v>0.16682886139302086</v>
+        <v>0.053623562590613842</v>
       </c>
       <c r="J85" s="0">
-        <v>0.4600662495399333</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K85" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L85" s="0">
-        <v>0.28457686685534761</v>
+        <v>0.083973501695020617</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.22644481638278999</v>
+        <v>0.095992911292704458</v>
       </c>
       <c r="B86" s="0">
-        <v>0.43859649122806976</v>
+        <v>0</v>
       </c>
       <c r="C86" s="0">
-        <v>0.10144688621463616</v>
+        <v>0.0050723443107318078</v>
       </c>
       <c r="D86" s="0">
-        <v>0.11299978361743553</v>
+        <v>0.040872262159497956</v>
       </c>
       <c r="E86" s="0">
-        <v>0.13484889167337916</v>
+        <v>0.078761299561442691</v>
       </c>
       <c r="F86" s="0">
-        <v>0.33293308590765169</v>
+        <v>0.10006185642033248</v>
       </c>
       <c r="G86" s="0">
-        <v>0.22128344397505512</v>
+        <v>0</v>
       </c>
       <c r="H86" s="0">
-        <v>0.19314889507470301</v>
+        <v>0.26699994319150122</v>
       </c>
       <c r="I86" s="0">
-        <v>0.14299616690830358</v>
+        <v>0.047665388969434529</v>
       </c>
       <c r="J86" s="0">
-        <v>0.331247699668752</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K86" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L86" s="0">
-        <v>0.21926414331477603</v>
+        <v>0.068422853232979752</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.20429260608447358</v>
+        <v>0.11076105149158205</v>
       </c>
       <c r="B87" s="0">
-        <v>0</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C87" s="0">
-        <v>0.071012820350245323</v>
+        <v>0.010144688621463616</v>
       </c>
       <c r="D87" s="0">
-        <v>0.11299978361743553</v>
+        <v>0.028851008583175027</v>
       </c>
       <c r="E87" s="0">
-        <v>0.10561174259375269</v>
+        <v>0.065037739789373133</v>
       </c>
       <c r="F87" s="0">
-        <v>0.28381181093767033</v>
+        <v>0.058217807371829799</v>
       </c>
       <c r="G87" s="0">
-        <v>0.12070006035003007</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H87" s="0">
-        <v>0.19882974492984132</v>
+        <v>0.16474464579901138</v>
       </c>
       <c r="I87" s="0">
-        <v>0.10128895156004836</v>
+        <v>0.017874520863537947</v>
       </c>
       <c r="J87" s="0">
-        <v>0.25763709974236265</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K87" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L87" s="0">
-        <v>0.22237427300718421</v>
+        <v>0.045096880539918477</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.19690853598503477</v>
+        <v>0.066456630894949242</v>
       </c>
       <c r="B88" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C88" s="0">
-        <v>0.067208562117196446</v>
+        <v>0.0038042582330488559</v>
       </c>
       <c r="D88" s="0">
-        <v>0.074531772173202157</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E88" s="0">
-        <v>0.093081535845341373</v>
+        <v>0.054894239088278243</v>
       </c>
       <c r="F88" s="0">
-        <v>0.26379943965360381</v>
+        <v>0.052759887930720763</v>
       </c>
       <c r="G88" s="0">
-        <v>0.20116676725005009</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H88" s="0">
-        <v>0.19314889507470301</v>
+        <v>0.090893597682213168</v>
       </c>
       <c r="I88" s="0">
-        <v>0.097316835812595495</v>
+        <v>0.011916347242358632</v>
       </c>
       <c r="J88" s="0">
-        <v>0.25763709974236265</v>
+        <v>0.073610599926389339</v>
       </c>
       <c r="K88" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L88" s="0">
-        <v>0.17727739246726573</v>
+        <v>0.024881037539265367</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.18460175248597011</v>
+        <v>0.039381707197006954</v>
       </c>
       <c r="B89" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C89" s="0">
-        <v>0.04565109879658627</v>
+        <v>0.0063404303884147598</v>
       </c>
       <c r="D89" s="0">
-        <v>0.10819128218690635</v>
+        <v>0.016829755006852101</v>
       </c>
       <c r="E89" s="0">
-        <v>0.076971270025955357</v>
+        <v>0.035203914197917567</v>
       </c>
       <c r="F89" s="0">
-        <v>0.20740093876214369</v>
+        <v>0.0291089036859149</v>
       </c>
       <c r="G89" s="0">
-        <v>0.18105009052504509</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H89" s="0">
-        <v>0.22155314435039461</v>
+        <v>0.085212747827074858</v>
       </c>
       <c r="I89" s="0">
-        <v>0.069512025580425352</v>
+        <v>0.01390240511608507</v>
       </c>
       <c r="J89" s="0">
-        <v>0.14722119985277868</v>
+        <v>0.03680529996319467</v>
       </c>
       <c r="K89" s="0">
-        <v>0.25773195876288635</v>
+        <v>1.2886597938144317</v>
       </c>
       <c r="L89" s="0">
-        <v>0.14306596585077586</v>
+        <v>0.017105713308244938</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.12306783499064673</v>
+        <v>0.03199763709756815</v>
       </c>
       <c r="B90" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C90" s="0">
-        <v>0.040578754485854462</v>
+        <v>0</v>
       </c>
       <c r="D90" s="0">
-        <v>0.086553025749525073</v>
+        <v>0</v>
       </c>
       <c r="E90" s="0">
-        <v>0.044154061875354242</v>
+        <v>0.025657090008651785</v>
       </c>
       <c r="F90" s="0">
-        <v>0.15827966379216227</v>
+        <v>0.025470290725175541</v>
       </c>
       <c r="G90" s="0">
-        <v>0.14081673707503506</v>
+        <v>0</v>
       </c>
       <c r="H90" s="0">
-        <v>0.10793614724762815</v>
+        <v>0.073851048116798199</v>
       </c>
       <c r="I90" s="0">
-        <v>0.043693273221981653</v>
+        <v>0.01390240511608507</v>
       </c>
       <c r="J90" s="0">
-        <v>0.20242914979757068</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K90" s="0">
-        <v>0.25773195876288635</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L90" s="0">
-        <v>0.087083631387428778</v>
+        <v>0.024881037539265367</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.12552919169045967</v>
+        <v>0.029536280397755216</v>
       </c>
       <c r="B91" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C91" s="0">
-        <v>0.022825549398293135</v>
+        <v>0</v>
       </c>
       <c r="D91" s="0">
-        <v>0.074531772173202157</v>
+        <v>0.012021253576322928</v>
       </c>
       <c r="E91" s="0">
-        <v>0.042364032339866901</v>
+        <v>0.014320236283898672</v>
       </c>
       <c r="F91" s="0">
-        <v>0.11279700178292025</v>
+        <v>0.0036386129607393625</v>
       </c>
       <c r="G91" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H91" s="0">
-        <v>0.11361699710276646</v>
+        <v>0.06817019826165989</v>
       </c>
       <c r="I91" s="0">
-        <v>0.037735099600802333</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J91" s="0">
-        <v>0.165623849834376</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K91" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.417525773195875</v>
       </c>
       <c r="L91" s="0">
-        <v>0.06997791807918384</v>
+        <v>0.0062202593848163417</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.071379344294575112</v>
+        <v>0.014768140198877608</v>
       </c>
       <c r="B92" s="0">
-        <v>0</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C92" s="0">
-        <v>0.013948946854512471</v>
+        <v>0</v>
       </c>
       <c r="D92" s="0">
-        <v>0.036063760728968788</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E92" s="0">
-        <v>0.032220531638772011</v>
+        <v>0.011336853724753116</v>
       </c>
       <c r="F92" s="0">
-        <v>0.089146017538114394</v>
+        <v>0</v>
       </c>
       <c r="G92" s="0">
         <v>0.040233353450010022</v>
       </c>
       <c r="H92" s="0">
-        <v>0.10793614724762815</v>
+        <v>0.022723399420553292</v>
       </c>
       <c r="I92" s="0">
-        <v>0.023832694484717264</v>
+        <v>0.0079442314949057548</v>
       </c>
       <c r="J92" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K92" s="0">
-        <v>0.64432989690721587</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L92" s="0">
-        <v>0.052872204770938902</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.041843063896819889</v>
+        <v>0.0073840700994388039</v>
       </c>
       <c r="B93" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C93" s="0">
-        <v>0.010144688621463616</v>
+        <v>0</v>
       </c>
       <c r="D93" s="0">
-        <v>0.040872262159497956</v>
+        <v>0</v>
       </c>
       <c r="E93" s="0">
-        <v>0.016706942331215117</v>
+        <v>0.0047734120946328904</v>
       </c>
       <c r="F93" s="0">
-        <v>0.078230178655896293</v>
+        <v>0</v>
       </c>
       <c r="G93" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H93" s="0">
-        <v>0.085212747827074858</v>
+        <v>0.028404249275691615</v>
       </c>
       <c r="I93" s="0">
-        <v>0.019860578737264385</v>
+        <v>0</v>
       </c>
       <c r="J93" s="0">
-        <v>0.073610599926389339</v>
+        <v>0</v>
       </c>
       <c r="K93" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L93" s="0">
-        <v>0.038876621155102133</v>
+        <v>0.0046651945386122556</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.061533917495324046</v>
+        <v>0.0049227133996259239</v>
       </c>
       <c r="B94" s="0">
-        <v>0.087719298245614932</v>
+        <v>0.17543859649122986</v>
       </c>
       <c r="C94" s="0">
-        <v>0.0076085164660977958</v>
+        <v>0</v>
       </c>
       <c r="D94" s="0">
-        <v>0.033659510013704576</v>
+        <v>0</v>
       </c>
       <c r="E94" s="0">
-        <v>0.011336853724753241</v>
+        <v>0.0029833825591455898</v>
       </c>
       <c r="F94" s="0">
-        <v>0.045482662009242537</v>
+        <v>0</v>
       </c>
       <c r="G94" s="0">
-        <v>0.060350030175015702</v>
+        <v>0</v>
       </c>
       <c r="H94" s="0">
-        <v>0.034085099130830319</v>
+        <v>0.028404249275691931</v>
       </c>
       <c r="I94" s="0">
-        <v>0.011916347242358764</v>
+        <v>0</v>
       </c>
       <c r="J94" s="0">
-        <v>0.09201324990798769</v>
+        <v>0</v>
       </c>
       <c r="K94" s="0">
-        <v>1.67525773195878</v>
+        <v>1.4175257731958908</v>
       </c>
       <c r="L94" s="0">
-        <v>0.026436102385469746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.039381707197006954</v>
+        <v>0</v>
       </c>
       <c r="B95" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C95" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0</v>
       </c>
       <c r="D95" s="0">
-        <v>0.019234005722116688</v>
+        <v>0</v>
       </c>
       <c r="E95" s="0">
-        <v>0.0083534711656075584</v>
+        <v>0.0023867060473164452</v>
       </c>
       <c r="F95" s="0">
-        <v>0.025470290725175541</v>
+        <v>0</v>
       </c>
       <c r="G95" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H95" s="0">
-        <v>0.022723399420553292</v>
+        <v>0.011361699710276646</v>
       </c>
       <c r="I95" s="0">
-        <v>0.011916347242358632</v>
+        <v>0</v>
       </c>
       <c r="J95" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K95" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L95" s="0">
-        <v>0.007775324231020426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.027074923697942281</v>
+        <v>0</v>
       </c>
       <c r="B96" s="0">
-        <v>0.35087719298245584</v>
+        <v>0</v>
       </c>
       <c r="C96" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0</v>
       </c>
       <c r="D96" s="0">
-        <v>0.016829755006852101</v>
+        <v>0</v>
       </c>
       <c r="E96" s="0">
-        <v>0.007160118141949336</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F96" s="0">
-        <v>0.01273514536258777</v>
+        <v>0</v>
       </c>
       <c r="G96" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H96" s="0">
-        <v>0.034085099130829945</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I96" s="0">
         <v>0</v>
       </c>
       <c r="J96" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K96" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L96" s="0">
-        <v>0.0046651945386122556</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.012306783499064673</v>
+        <v>0</v>
       </c>
       <c r="B97" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C97" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D97" s="0">
-        <v>0.004808501430529172</v>
+        <v>0</v>
       </c>
       <c r="E97" s="0">
         <v>0</v>
       </c>
       <c r="F97" s="0">
-        <v>0.021831677764436178</v>
+        <v>0</v>
       </c>
       <c r="G97" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H97" s="0">
         <v>0.011361699710276646</v>
@@ -3747,86 +3748,86 @@
         <v>0</v>
       </c>
       <c r="J97" s="0">
-        <v>0.03680529996319467</v>
+        <v>0</v>
       </c>
       <c r="K97" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L97" s="0">
-        <v>0.0093303890772245112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.0098454267992517386</v>
+        <v>0</v>
       </c>
       <c r="B98" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C98" s="0">
         <v>0</v>
       </c>
       <c r="D98" s="0">
-        <v>0.012021253576322928</v>
+        <v>0</v>
       </c>
       <c r="E98" s="0">
-        <v>0.0011933530236582226</v>
+        <v>0</v>
       </c>
       <c r="F98" s="0">
-        <v>0.0054579194411090446</v>
+        <v>0</v>
       </c>
       <c r="G98" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H98" s="0">
         <v>0</v>
       </c>
       <c r="I98" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J98" s="0">
         <v>0</v>
       </c>
       <c r="K98" s="0">
-        <v>1.417525773195875</v>
+        <v>0</v>
       </c>
       <c r="L98" s="0">
-        <v>0.0031101296924081708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B99" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C99" s="0">
         <v>0</v>
       </c>
       <c r="D99" s="0">
-        <v>0.002404250715264586</v>
+        <v>0</v>
       </c>
       <c r="E99" s="0">
         <v>0</v>
       </c>
       <c r="F99" s="0">
-        <v>0.0054579194411090446</v>
+        <v>0</v>
       </c>
       <c r="G99" s="0">
         <v>0</v>
       </c>
       <c r="H99" s="0">
-        <v>0.017042549565414972</v>
+        <v>0</v>
       </c>
       <c r="I99" s="0">
-        <v>0.0039721157474528774</v>
+        <v>0</v>
       </c>
       <c r="J99" s="0">
         <v>0</v>
       </c>
       <c r="K99" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L99" s="0">
         <v>0</v>
@@ -3834,40 +3835,40 @@
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B100" s="0">
-        <v>1.0526315789473675</v>
+        <v>0</v>
       </c>
       <c r="C100" s="0">
         <v>0</v>
       </c>
       <c r="D100" s="0">
-        <v>0.002404250715264586</v>
+        <v>0</v>
       </c>
       <c r="E100" s="0">
-        <v>0.0011933530236582226</v>
+        <v>0</v>
       </c>
       <c r="F100" s="0">
-        <v>0.0072772259214787249</v>
+        <v>0</v>
       </c>
       <c r="G100" s="0">
         <v>0</v>
       </c>
       <c r="H100" s="0">
-        <v>0.005680849855138323</v>
+        <v>0</v>
       </c>
       <c r="I100" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J100" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K100" s="0">
-        <v>1.417525773195875</v>
+        <v>0</v>
       </c>
       <c r="L100" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0008_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0008_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
